--- a/特殊（とくしゅ）.xlsx
+++ b/特殊（とくしゅ）.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="758">
   <si>
     <t>裏口</t>
   </si>
@@ -4827,6 +4827,129 @@
     <t>（抄写）</t>
   </si>
   <si>
+    <t>在庫</t>
+  </si>
+  <si>
+    <t>ざいこ</t>
+  </si>
+  <si>
+    <t>（存货）</t>
+  </si>
+  <si>
+    <t>視聴</t>
+  </si>
+  <si>
+    <t>しちょう</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>（收看</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>电视）</t>
+    </r>
+  </si>
+  <si>
+    <t>戸棚</t>
+  </si>
+  <si>
+    <t>とだな</t>
+  </si>
+  <si>
+    <t>（柜子）</t>
+  </si>
+  <si>
+    <t>座敷</t>
+  </si>
+  <si>
+    <t>ざしき</t>
+  </si>
+  <si>
+    <t>（房间）</t>
+  </si>
+  <si>
+    <t>落第</t>
+  </si>
+  <si>
+    <t>らくだい</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>（留</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>级）</t>
+    </r>
+  </si>
+  <si>
+    <t>退社</t>
+  </si>
+  <si>
+    <t>たいしゃ</t>
+  </si>
+  <si>
+    <t>（辞职）</t>
+  </si>
+  <si>
+    <t>辞職</t>
+  </si>
+  <si>
+    <t>じしょく</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>（大老板</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>离职）</t>
+    </r>
+  </si>
+  <si>
+    <t>辞退</t>
+  </si>
+  <si>
+    <t>じたい</t>
+  </si>
+  <si>
+    <t>（礼貌拒绝）</t>
+  </si>
+  <si>
     <t>寿退社</t>
   </si>
   <si>
@@ -4853,57 +4976,22 @@
     </r>
   </si>
   <si>
-    <t>在庫</t>
-  </si>
-  <si>
-    <t>ざいこ</t>
-  </si>
-  <si>
-    <t>（存货）</t>
-  </si>
-  <si>
-    <t>視聴</t>
-  </si>
-  <si>
-    <t>しちょう</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <charset val="128"/>
-      </rPr>
-      <t>（收看</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="128"/>
-      </rPr>
-      <t>电视）</t>
-    </r>
-  </si>
-  <si>
-    <t>戸棚</t>
-  </si>
-  <si>
-    <t>とだな</t>
-  </si>
-  <si>
-    <t>（柜子）</t>
-  </si>
-  <si>
-    <t>座敷</t>
-  </si>
-  <si>
-    <t>ざしき</t>
-  </si>
-  <si>
-    <t>（房间）</t>
+    <t>障子</t>
+  </si>
+  <si>
+    <t>しょうじ</t>
+  </si>
+  <si>
+    <t>（拉窗，拉门）</t>
+  </si>
+  <si>
+    <t>用心深い</t>
+  </si>
+  <si>
+    <t>ようじんぶかい</t>
+  </si>
+  <si>
+    <t>（小心谨慎）</t>
   </si>
   <si>
     <t>評判</t>
@@ -5963,7 +6051,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:E244"/>
+  <dimension ref="A2:E251"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="18.3333333333333" style="1" customWidth="1"/>
@@ -8625,7 +8713,7 @@
       <c r="B240" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="C240" s="1" t="s">
+      <c r="C240" s="3" t="s">
         <v>711</v>
       </c>
     </row>
@@ -8636,18 +8724,18 @@
       <c r="B241" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="C241" s="3" t="s">
+      <c r="C241" s="1" t="s">
         <v>714</v>
       </c>
     </row>
     <row r="242" spans="1:3">
-      <c r="A242" s="1" t="s">
+      <c r="A242" s="10" t="s">
         <v>715</v>
       </c>
-      <c r="B242" s="1" t="s">
+      <c r="B242" s="10" t="s">
         <v>716</v>
       </c>
-      <c r="C242" s="1" t="s">
+      <c r="C242" t="s">
         <v>717</v>
       </c>
     </row>
@@ -8663,14 +8751,91 @@
       </c>
     </row>
     <row r="244" spans="1:3">
-      <c r="A244" s="10" t="s">
+      <c r="A244" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="B244" s="10" t="s">
+      <c r="B244" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="C244" t="s">
+      <c r="C244" s="1" t="s">
         <v>723</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3">
+      <c r="A245" t="s">
+        <v>724</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="C245" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3">
+      <c r="A246" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3">
+      <c r="A247" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C247" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3">
+      <c r="A248" t="s">
+        <v>730</v>
+      </c>
+      <c r="B248" t="s">
+        <v>731</v>
+      </c>
+      <c r="C248" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3">
+      <c r="A249" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3">
+      <c r="A250" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3">
+      <c r="A251" t="s">
+        <v>739</v>
+      </c>
+      <c r="B251" t="s">
+        <v>740</v>
+      </c>
+      <c r="C251" t="s">
+        <v>741</v>
       </c>
     </row>
   </sheetData>
@@ -8690,10 +8855,10 @@
   <sheetData>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>724</v>
+        <v>742</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>725</v>
+        <v>743</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8717,34 +8882,34 @@
         <v>166</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>726</v>
+        <v>744</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>727</v>
+        <v>745</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>728</v>
+        <v>746</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>729</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>730</v>
+        <v>748</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>731</v>
+        <v>749</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>732</v>
+        <v>750</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>733</v>
+        <v>751</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8757,26 +8922,26 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>734</v>
+        <v>752</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>735</v>
+        <v>753</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>736</v>
+        <v>754</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>737</v>
+        <v>755</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>738</v>
+        <v>756</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>739</v>
+        <v>757</v>
       </c>
     </row>
     <row r="13" spans="1:3">

--- a/特殊（とくしゅ）.xlsx
+++ b/特殊（とくしゅ）.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="767">
   <si>
     <t>裏口</t>
   </si>
@@ -4992,6 +4992,33 @@
   </si>
   <si>
     <t>（小心谨慎）</t>
+  </si>
+  <si>
+    <t>値下り</t>
+  </si>
+  <si>
+    <t>ねさがり</t>
+  </si>
+  <si>
+    <t>（跌价）</t>
+  </si>
+  <si>
+    <t>人目</t>
+  </si>
+  <si>
+    <t>ひとめ</t>
+  </si>
+  <si>
+    <t>（世俗的眼光）</t>
+  </si>
+  <si>
+    <t>整髪料</t>
+  </si>
+  <si>
+    <t>せいはつりょう</t>
+  </si>
+  <si>
+    <t>（洗发水）</t>
   </si>
   <si>
     <t>評判</t>
@@ -6051,7 +6078,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:E251"/>
+  <dimension ref="A2:E254"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="18.3333333333333" style="1" customWidth="1"/>
@@ -8836,6 +8863,39 @@
       </c>
       <c r="C251" t="s">
         <v>741</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3">
+      <c r="A252" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3">
+      <c r="A253" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3">
+      <c r="A254" t="s">
+        <v>748</v>
+      </c>
+      <c r="B254" t="s">
+        <v>749</v>
+      </c>
+      <c r="C254" t="s">
+        <v>750</v>
       </c>
     </row>
   </sheetData>
@@ -8855,10 +8915,10 @@
   <sheetData>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>742</v>
+        <v>751</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>743</v>
+        <v>752</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8882,34 +8942,34 @@
         <v>166</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>744</v>
+        <v>753</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>745</v>
+        <v>754</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>746</v>
+        <v>755</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>747</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>748</v>
+        <v>757</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>749</v>
+        <v>758</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>750</v>
+        <v>759</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>751</v>
+        <v>760</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8922,26 +8982,26 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>752</v>
+        <v>761</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>753</v>
+        <v>762</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>754</v>
+        <v>763</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>755</v>
+        <v>764</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>756</v>
+        <v>765</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>757</v>
+        <v>766</v>
       </c>
     </row>
     <row r="13" spans="1:3">

--- a/特殊（とくしゅ）.xlsx
+++ b/特殊（とくしゅ）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="784">
   <si>
     <t>裏口</t>
   </si>
@@ -5019,6 +5019,77 @@
   </si>
   <si>
     <t>（洗发水）</t>
+  </si>
+  <si>
+    <t>事柄</t>
+  </si>
+  <si>
+    <t>ことがら</t>
+  </si>
+  <si>
+    <t>（事情）</t>
+  </si>
+  <si>
+    <t>用件</t>
+  </si>
+  <si>
+    <t>ようけん</t>
+  </si>
+  <si>
+    <t>急用</t>
+  </si>
+  <si>
+    <t>きゅうよう</t>
+  </si>
+  <si>
+    <r>
+      <t>（急事，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>紧</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>急的事情）</t>
+    </r>
+  </si>
+  <si>
+    <t>噓つき</t>
+  </si>
+  <si>
+    <t>うそつき</t>
+  </si>
+  <si>
+    <t>（喜欢说谎的人）</t>
+  </si>
+  <si>
+    <t>昇進</t>
+  </si>
+  <si>
+    <t>しょうしん</t>
+  </si>
+  <si>
+    <t>（晋升）</t>
+  </si>
+  <si>
+    <t>水道水</t>
+  </si>
+  <si>
+    <t>すいどうすい</t>
+  </si>
+  <si>
+    <t>（自来水）</t>
   </si>
   <si>
     <t>評判</t>
@@ -6078,7 +6149,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:E254"/>
+  <dimension ref="A2:E260"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="18.3333333333333" style="1" customWidth="1"/>
@@ -8896,6 +8967,72 @@
       </c>
       <c r="C254" t="s">
         <v>750</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3">
+      <c r="A255" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3">
+      <c r="A256" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3">
+      <c r="A257" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3">
+      <c r="A258" t="s">
+        <v>759</v>
+      </c>
+      <c r="B258" t="s">
+        <v>760</v>
+      </c>
+      <c r="C258" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3">
+      <c r="A259" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3">
+      <c r="A260" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>767</v>
       </c>
     </row>
   </sheetData>
@@ -8915,10 +9052,10 @@
   <sheetData>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>751</v>
+        <v>768</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>752</v>
+        <v>769</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8942,34 +9079,34 @@
         <v>166</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>753</v>
+        <v>770</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>754</v>
+        <v>771</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>755</v>
+        <v>772</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>756</v>
+        <v>773</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>757</v>
+        <v>774</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>758</v>
+        <v>775</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>759</v>
+        <v>776</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>760</v>
+        <v>777</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8982,26 +9119,26 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>761</v>
+        <v>778</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>762</v>
+        <v>779</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>763</v>
+        <v>780</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>764</v>
+        <v>781</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>765</v>
+        <v>782</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>766</v>
+        <v>783</v>
       </c>
     </row>
     <row r="13" spans="1:3">

--- a/特殊（とくしゅ）.xlsx
+++ b/特殊（とくしゅ）.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="787">
   <si>
     <t>裏口</t>
   </si>
@@ -5043,6 +5043,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
       <t>（急事，</t>
     </r>
     <r>
@@ -5090,6 +5096,15 @@
   </si>
   <si>
     <t>（自来水）</t>
+  </si>
+  <si>
+    <t>同窓会</t>
+  </si>
+  <si>
+    <t>どうそうかい</t>
+  </si>
+  <si>
+    <t>（同学会）</t>
   </si>
   <si>
     <t>評判</t>
@@ -6149,7 +6164,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:E260"/>
+  <dimension ref="A2:E261"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="18.3333333333333" style="1" customWidth="1"/>
@@ -9033,6 +9048,17 @@
       </c>
       <c r="C260" s="1" t="s">
         <v>767</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3">
+      <c r="A261" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>770</v>
       </c>
     </row>
   </sheetData>
@@ -9052,10 +9078,10 @@
   <sheetData>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9079,34 +9105,34 @@
         <v>166</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -9119,26 +9145,26 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
     </row>
     <row r="13" spans="1:3">

--- a/特殊（とくしゅ）.xlsx
+++ b/特殊（とくしゅ）.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="797">
   <si>
     <t>裏口</t>
   </si>
@@ -5107,6 +5107,41 @@
     <t>（同学会）</t>
   </si>
   <si>
+    <t>繊維</t>
+  </si>
+  <si>
+    <t>せんい</t>
+  </si>
+  <si>
+    <t>（纤维）</t>
+  </si>
+  <si>
+    <t>めちゃめちゃ</t>
+  </si>
+  <si>
+    <t>（一塌糊涂）</t>
+  </si>
+  <si>
+    <t>見出し</t>
+  </si>
+  <si>
+    <t>みだし</t>
+  </si>
+  <si>
+    <r>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>标题）</t>
+    </r>
+  </si>
+  <si>
     <t>評判</t>
   </si>
   <si>
@@ -5153,6 +5188,12 @@
   </si>
   <si>
     <t>しらが</t>
+  </si>
+  <si>
+    <t>前非</t>
+  </si>
+  <si>
+    <t>ぜんぴ</t>
   </si>
 </sst>
 </file>
@@ -6164,7 +6205,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:E261"/>
+  <dimension ref="A2:E264"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="18.3333333333333" style="1" customWidth="1"/>
@@ -9061,6 +9102,39 @@
         <v>770</v>
       </c>
     </row>
+    <row r="262" spans="1:3">
+      <c r="A262" t="s">
+        <v>771</v>
+      </c>
+      <c r="B262" t="s">
+        <v>772</v>
+      </c>
+      <c r="C262" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3">
+      <c r="A263" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3">
+      <c r="A264" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>778</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -9070,7 +9144,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:C13"/>
+  <dimension ref="A2:C14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="16384" width="8.88888888888889" style="1"/>
@@ -9078,10 +9152,10 @@
   <sheetData>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9105,34 +9179,34 @@
         <v>166</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -9145,26 +9219,26 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9173,6 +9247,14 @@
       </c>
       <c r="B13" s="1" t="s">
         <v>295</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>796</v>
       </c>
     </row>
   </sheetData>

--- a/特殊（とくしゅ）.xlsx
+++ b/特殊（とくしゅ）.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="805">
   <si>
     <t>裏口</t>
   </si>
@@ -5129,6 +5129,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
       <t>（</t>
     </r>
     <r>
@@ -5140,6 +5146,30 @@
       </rPr>
       <t>标题）</t>
     </r>
+  </si>
+  <si>
+    <t>口振り</t>
+  </si>
+  <si>
+    <t>くちぶり</t>
+  </si>
+  <si>
+    <t>（说话时的语气）</t>
+  </si>
+  <si>
+    <t>針路</t>
+  </si>
+  <si>
+    <t>しんろ</t>
+  </si>
+  <si>
+    <t>（方向点，航向，方向）</t>
+  </si>
+  <si>
+    <t>おもけ</t>
+  </si>
+  <si>
+    <t>（赠品，附录）</t>
   </si>
   <si>
     <t>評判</t>
@@ -6205,7 +6235,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:E264"/>
+  <dimension ref="A2:E267"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="18.3333333333333" style="1" customWidth="1"/>
@@ -9047,7 +9077,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="257" spans="1:3">
+    <row r="257" spans="1:4">
       <c r="A257" s="1" t="s">
         <v>756</v>
       </c>
@@ -9058,7 +9088,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="258" spans="1:3">
+    <row r="258" spans="1:4">
       <c r="A258" t="s">
         <v>759</v>
       </c>
@@ -9069,7 +9099,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="259" spans="1:3">
+    <row r="259" spans="1:4">
       <c r="A259" s="1" t="s">
         <v>762</v>
       </c>
@@ -9080,7 +9110,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="260" spans="1:3">
+    <row r="260" spans="1:4">
       <c r="A260" s="1" t="s">
         <v>765</v>
       </c>
@@ -9091,7 +9121,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="261" spans="1:3">
+    <row r="261" spans="1:4">
       <c r="A261" s="1" t="s">
         <v>768</v>
       </c>
@@ -9102,7 +9132,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="262" spans="1:3">
+    <row r="262" spans="1:4">
       <c r="A262" t="s">
         <v>771</v>
       </c>
@@ -9113,7 +9143,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="263" spans="1:3">
+    <row r="263" spans="1:4">
       <c r="A263" s="1" t="s">
         <v>690</v>
       </c>
@@ -9124,7 +9154,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="264" spans="1:3">
+    <row r="264" spans="1:4">
       <c r="A264" s="1" t="s">
         <v>776</v>
       </c>
@@ -9134,6 +9164,37 @@
       <c r="C264" s="1" t="s">
         <v>778</v>
       </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" t="s">
+        <v>779</v>
+      </c>
+      <c r="B265" t="s">
+        <v>780</v>
+      </c>
+      <c r="C265" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="B267" t="s">
+        <v>785</v>
+      </c>
+      <c r="C267" t="s">
+        <v>786</v>
+      </c>
+      <c r="D267"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9152,10 +9213,10 @@
   <sheetData>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9179,34 +9240,34 @@
         <v>166</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -9219,26 +9280,26 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>794</v>
+        <v>802</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9251,10 +9312,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
     </row>
   </sheetData>
